--- a/public/templates/forms/A-027-CybersecurityBudgetResourceAllocationRecord-FORM.xlsx
+++ b/public/templates/forms/A-027-CybersecurityBudgetResourceAllocationRecord-FORM.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -60,8 +60,31 @@
       <color rgb="FF000000"/>
       <sz val="12"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF595959"/>
+      <name val="Aptos"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -84,6 +107,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFF4F1E8"/>
         <bgColor rgb="FFEEF2F7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B3A5C"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -158,7 +187,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -201,6 +230,18 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -814,7 +855,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>Indiana statutes and administrative code: IC 36-8-16.7 — allowable uses of statewide 911 fund distributions</t>
+          <t>Indiana statutes and administrative code: IC 36-8-16.7: allowable uses of statewide 911 fund distributions</t>
         </is>
       </c>
     </row>
@@ -926,7 +967,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1117,11 +1158,79 @@
         </is>
       </c>
     </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Profile Scaling Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">What minimum-viable upkeep looks like at each PSAP size. Keep all three rows while this ships as a template; once adopted, keep the one that fits.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSAP Profile</t>
+        </is>
+      </c>
+      <c r="B16" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Minimum-viable implementation</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="42" customHeight="1">
+      <c r="A17" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Small (1–5, no in-house IT)</t>
+        </is>
+      </c>
+      <c r="B17" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Maintain this by hand. One person, usually the director, keeps it current on the review cycle in the header block.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="42" customHeight="1">
+      <c r="A18" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medium (6–25, shared county IT)</t>
+        </is>
+      </c>
+      <c r="B18" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A named coordinator owns it, updates it on a set cadence, and reconciles it at each periodic review.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="42" customHeight="1">
+      <c r="A19" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Large (25+, dedicated IT/security)</t>
+        </is>
+      </c>
+      <c r="B19" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Where a system of record exists (asset, identity, badge, or finance system), populate it from there on a schedule and treat this sheet as the reviewed record.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="9">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="B19:D19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" fitToHeight="0" horizontalDpi="300" verticalDpi="300"/>

--- a/public/templates/forms/A-027-CybersecurityBudgetResourceAllocationRecord-FORM.xlsx
+++ b/public/templates/forms/A-027-CybersecurityBudgetResourceAllocationRecord-FORM.xlsx
@@ -19,7 +19,7 @@
   <numFmts count="0"/>
   <fonts count="11">
     <font>
-      <name val="Calibri"/>
+      <name val="Aptos"/>
       <charset val="1"/>
       <family val="2"/>
       <color theme="1"/>
@@ -361,12 +361,12 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Aptos"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Aptos"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>

--- a/public/templates/forms/A-027-CybersecurityBudgetResourceAllocationRecord-FORM.xlsx
+++ b/public/templates/forms/A-027-CybersecurityBudgetResourceAllocationRecord-FORM.xlsx
@@ -3,12 +3,15 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="720" yWindow="780" windowWidth="23380" windowHeight="21660" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="720" yWindow="780" windowWidth="23380" windowHeight="21660" tabRatio="500" firstSheet="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ledger" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Column Instructions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">Ledger!$11:$11</definedName>
+  </definedNames>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -537,7 +540,7 @@
       <c r="E3" s="17" t="n"/>
       <c r="F3" s="16" t="n"/>
     </row>
-    <row r="4" ht="15" customHeight="1">
+    <row r="4" ht="34.7" customHeight="1">
       <c r="A4" s="7" t="inlineStr">
         <is>
           <t>Owner</t>
@@ -585,7 +588,7 @@
       <c r="E6" s="17" t="n"/>
       <c r="F6" s="16" t="n"/>
     </row>
-    <row r="7" ht="30" customHeight="1">
+    <row r="7" ht="34.7" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Coverage / Cycle</t>
@@ -608,14 +611,14 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1">
+    <row r="10" ht="34.7" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
         <is>
           <t>« Add one row per budget line, allocation, or commitment. These columns are the standard minimum; add columns this ledger needs (e.g., spent-to-date, variance). »</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="27.75" customHeight="1">
+    <row r="11" ht="34.7" customHeight="1">
       <c r="A11" s="10" t="inlineStr">
         <is>
           <t>Entry #</t>
@@ -734,7 +737,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="29.75" customHeight="1">
+    <row r="24" ht="34.7" customHeight="1">
       <c r="A24" s="8" t="inlineStr">
         <is>
           <t>« Summarize total committed by cycle and category, and tie the allocation back to the Cybersecurity Charter / Leadership Designation Letter. Note any unfunded items and where they are tracked. »</t>
@@ -917,7 +920,7 @@
       <c r="E46" s="11" t="n"/>
       <c r="F46" s="11" t="n"/>
     </row>
-    <row r="48" ht="30" customHeight="1">
+    <row r="48" ht="66.4" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
           <t>Drafter's note (internal, delete before publishing): Ties the committed spend back to the Cybersecurity Charter / Leadership Designation Letter, and the dated entries support the annual leadership review recorded in the Leadership Security Review Meeting Minutes. Owner ships as a role; a PSAP may add a named individual, and must revise the record when that person changes. Confirm the NENA-STA-040.2-2024 section (§4.1.1) against the standard in force. Where 911 fund distributions are used, confirm the spend is an allowable use under IC 36-8-16.7.</t>
@@ -957,7 +960,7 @@
     <mergeCell ref="A25:F25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="landscape" fitToHeight="0" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
 </file>
 
@@ -990,7 +993,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="29.75" customHeight="1">
+    <row r="3" ht="34.7" customHeight="1">
       <c r="A3" s="8" t="inlineStr">
         <is>
           <t>Placeholder key:  [BRACKETED] = fill in   ·   « » = guidance to delete.  Classification, summary, sign-off, retention and revision history live on the Ledger tab.</t>
@@ -1070,7 +1073,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="30" customHeight="1">
+    <row r="9" ht="34.7" customHeight="1">
       <c r="A9" s="15" t="inlineStr">
         <is>
           <t>Line Item / Category</t>
@@ -1136,7 +1139,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="30" customHeight="1">
+    <row r="12" ht="34.7" customHeight="1">
       <c r="A12" s="15" t="inlineStr">
         <is>
           <t>Notes / Ties-to</t>
@@ -1233,6 +1236,6 @@
     <mergeCell ref="B19:D19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="landscape" fitToHeight="0" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
 </file>